--- a/learning-system.xlsx
+++ b/learning-system.xlsx
@@ -627,7 +627,7 @@
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5">
-        <f>IFERROR(F10/E10*(1+(1-G10)),0)</f>
+        <f>IFERROR(F10/E10*(1+G10),0)</f>
         <v/>
       </c>
     </row>
@@ -640,7 +640,7 @@
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5">
-        <f>IFERROR(F11/E11*(1+(1-G11)),0)</f>
+        <f>IFERROR(F11/E11*(1+G11),0)</f>
         <v/>
       </c>
     </row>
@@ -653,7 +653,7 @@
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5">
-        <f>IFERROR(F12/E12*(1+(1-G12)),0)</f>
+        <f>IFERROR(F12/E12*(1+G12),0)</f>
         <v/>
       </c>
     </row>
@@ -666,7 +666,7 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5">
-        <f>IFERROR(F13/E13*(1+(1-G13)),0)</f>
+        <f>IFERROR(F13/E13*(1+G13),0)</f>
         <v/>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5">
-        <f>IFERROR(F14/E14*(1+(1-G14)),0)</f>
+        <f>IFERROR(F14/E14*(1+G14),0)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5">
-        <f>IFERROR(F15/E15*(1+(1-G15)),0)</f>
+        <f>IFERROR(F15/E15*(1+G15),0)</f>
         <v/>
       </c>
     </row>
@@ -705,7 +705,7 @@
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5">
-        <f>IFERROR(F16/E16*(1+(1-G16)),0)</f>
+        <f>IFERROR(F16/E16*(1+G16),0)</f>
         <v/>
       </c>
     </row>
@@ -718,7 +718,7 @@
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5">
-        <f>IFERROR(F17/E17*(1+(1-G17)),0)</f>
+        <f>IFERROR(F17/E17*(1+G17),0)</f>
         <v/>
       </c>
     </row>
@@ -731,7 +731,7 @@
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5">
-        <f>IFERROR(F18/E18*(1+(1-G18)),0)</f>
+        <f>IFERROR(F18/E18*(1+G18),0)</f>
         <v/>
       </c>
     </row>
@@ -744,7 +744,7 @@
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5">
-        <f>IFERROR(F19/E19*(1+(1-G19)),0)</f>
+        <f>IFERROR(F19/E19*(1+G19),0)</f>
         <v/>
       </c>
     </row>
@@ -757,7 +757,7 @@
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5">
-        <f>IFERROR(F20/E20*(1+(1-G20)),0)</f>
+        <f>IFERROR(F20/E20*(1+G20),0)</f>
         <v/>
       </c>
     </row>
@@ -770,7 +770,7 @@
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5">
-        <f>IFERROR(F21/E21*(1+(1-G21)),0)</f>
+        <f>IFERROR(F21/E21*(1+G21),0)</f>
         <v/>
       </c>
     </row>
@@ -783,7 +783,7 @@
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5">
-        <f>IFERROR(F22/E22*(1+(1-G22)),0)</f>
+        <f>IFERROR(F22/E22*(1+G22),0)</f>
         <v/>
       </c>
     </row>
@@ -796,7 +796,7 @@
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5">
-        <f>IFERROR(F23/E23*(1+(1-G23)),0)</f>
+        <f>IFERROR(F23/E23*(1+G23),0)</f>
         <v/>
       </c>
     </row>
@@ -809,7 +809,7 @@
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5">
-        <f>IFERROR(F24/E24*(1+(1-G24)),0)</f>
+        <f>IFERROR(F24/E24*(1+G24),0)</f>
         <v/>
       </c>
     </row>
@@ -822,7 +822,7 @@
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5">
-        <f>IFERROR(F25/E25*(1+(1-G25)),0)</f>
+        <f>IFERROR(F25/E25*(1+G25),0)</f>
         <v/>
       </c>
     </row>
@@ -835,7 +835,7 @@
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5">
-        <f>IFERROR(F26/E26*(1+(1-G26)),0)</f>
+        <f>IFERROR(F26/E26*(1+G26),0)</f>
         <v/>
       </c>
     </row>
@@ -848,7 +848,7 @@
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5">
-        <f>IFERROR(F27/E27*(1+(1-G27)),0)</f>
+        <f>IFERROR(F27/E27*(1+G27),0)</f>
         <v/>
       </c>
     </row>
@@ -861,7 +861,7 @@
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5">
-        <f>IFERROR(F28/E28*(1+(1-G28)),0)</f>
+        <f>IFERROR(F28/E28*(1+G28),0)</f>
         <v/>
       </c>
     </row>
@@ -874,7 +874,7 @@
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5">
-        <f>IFERROR(F29/E29*(1+(1-G29)),0)</f>
+        <f>IFERROR(F29/E29*(1+G29),0)</f>
         <v/>
       </c>
     </row>
@@ -887,7 +887,7 @@
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5">
-        <f>IFERROR(F30/E30*(1+(1-G30)),0)</f>
+        <f>IFERROR(F30/E30*(1+G30),0)</f>
         <v/>
       </c>
     </row>
@@ -900,7 +900,7 @@
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5">
-        <f>IFERROR(F31/E31*(1+(1-G31)),0)</f>
+        <f>IFERROR(F31/E31*(1+G31),0)</f>
         <v/>
       </c>
     </row>
@@ -913,7 +913,7 @@
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5">
-        <f>IFERROR(F32/E32*(1+(1-G32)),0)</f>
+        <f>IFERROR(F32/E32*(1+G32),0)</f>
         <v/>
       </c>
     </row>
@@ -926,7 +926,7 @@
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5">
-        <f>IFERROR(F33/E33*(1+(1-G33)),0)</f>
+        <f>IFERROR(F33/E33*(1+G33),0)</f>
         <v/>
       </c>
     </row>
@@ -939,7 +939,7 @@
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5">
-        <f>IFERROR(F34/E34*(1+(1-G34)),0)</f>
+        <f>IFERROR(F34/E34*(1+G34),0)</f>
         <v/>
       </c>
     </row>
@@ -952,7 +952,7 @@
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5">
-        <f>IFERROR(F35/E35*(1+(1-G35)),0)</f>
+        <f>IFERROR(F35/E35*(1+G35),0)</f>
         <v/>
       </c>
     </row>
@@ -965,7 +965,7 @@
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5">
-        <f>IFERROR(F36/E36*(1+(1-G36)),0)</f>
+        <f>IFERROR(F36/E36*(1+G36),0)</f>
         <v/>
       </c>
     </row>
@@ -978,7 +978,7 @@
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5">
-        <f>IFERROR(F37/E37*(1+(1-G37)),0)</f>
+        <f>IFERROR(F37/E37*(1+G37),0)</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5">
-        <f>IFERROR(F38/E38*(1+(1-G38)),0)</f>
+        <f>IFERROR(F38/E38*(1+G38),0)</f>
         <v/>
       </c>
     </row>
@@ -1004,14 +1004,14 @@
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5">
-        <f>IFERROR(F39/E39*(1+(1-G39)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="42" customHeight="1">
+        <f>IFERROR(F39/E39*(1+G39),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="56" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Priority score = Importance ÷ Challenge × (1 + mastery gap) — note this is the inverse of the original spreadsheet's direction (which rewarded higher mastery); this version prioritizes what you know LEAST, weighted by how important and how hard it is. Sort this table descending on Priority score to get study order.</t>
+          <t>Priority score = Importance ÷ Challenge × (1 + %Mastered) — matches the original spreadsheet exactly. This is intentional, not a bug: it's part of the spaced-repetition framework — material you've already mastered still needs quick, high-priority review passes to lock in retention, so it stays in the active queue rather than dropping off once you know it. Sort this table descending on Priority score to get study order.</t>
         </is>
       </c>
     </row>
